--- a/VerveStacks_UZB_grids_kan15/Sets-vervestacks.xlsx
+++ b/VerveStacks_UZB_grids_kan15/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_UZB_grids_kan15\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A71ECAA-9426-4AE4-AD3C-B21A2F3CAE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36A3E4A-CD25-49C0-ABDC-12BA6D21B4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="1" r:id="rId1"/>
@@ -1296,25 +1296,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>128</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>130</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>132</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>134</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>136</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>bioenergy</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>137</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>hydrogen</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>120</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>nuclear</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>138</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>140</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>142</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>144</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>146</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>148</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>co2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>149</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>151</v>
       </c>
@@ -1472,14 +1472,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B9:E74"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>154</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>159</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>161</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>163</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>165</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>167</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>169</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>171</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>173</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>175</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>177</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>179</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>181</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>183</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>185</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>187</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>189</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>191</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>193</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>195</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>197</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>199</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>201</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>203</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>205</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>207</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>209</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>211</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>213</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>215</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>217</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>219</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>221</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>223</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>225</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>227</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>229</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>231</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>233</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>235</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>237</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>239</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>241</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>243</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>245</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>247</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>249</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>251</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>253</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>255</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>257</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>259</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>261</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>263</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>265</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>267</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>269</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>271</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>273</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>275</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>277</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>279</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>281</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>283</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>285</v>
       </c>
@@ -2397,26 +2397,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J47"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.59765625" customWidth="1"/>
-    <col min="3" max="3" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5703125" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:10" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
         <v>66</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>69</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
         <v>72</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>91</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -2869,12 +2869,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:10" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>1</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>104</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>106</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>106</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>111</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>113</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>115</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>distr_sol</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>116</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>distr_won</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>117</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>distr_wof</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D44" t="s">
         <v>118</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>hs_geothermal</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D45" t="s">
         <v>119</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>hs_hydro</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D46" t="s">
         <v>120</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>hs_nuclear</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D47" t="s">
         <v>121</v>
       </c>
